--- a/regression_deneme/regression_with_nn/gaziemir_weekly_true_and_predicted_test.xlsx
+++ b/regression_deneme/regression_with_nn/gaziemir_weekly_true_and_predicted_test.xlsx
@@ -461,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.427571934084575</v>
+        <v>1.91797375363923</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +475,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>11.73327192430876</v>
+        <v>9.188746496832824</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>5.705869224470888</v>
+        <v>10.99142044929242</v>
       </c>
     </row>
     <row r="5">
@@ -503,7 +503,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>11.04592989272297</v>
+        <v>11.56373835114639</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>7.755964641816706</v>
+        <v>11.45500547579373</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8.96965086177039</v>
+        <v>9.670213196317198</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>8.819358330797916</v>
+        <v>9.860719674593742</v>
       </c>
     </row>
     <row r="9">
@@ -559,7 +559,7 @@
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>11.28461913268074</v>
+        <v>11.5695768064542</v>
       </c>
     </row>
     <row r="10">
@@ -573,7 +573,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>13.67584593468483</v>
+        <v>13.63957614874273</v>
       </c>
     </row>
     <row r="11">
@@ -587,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>13.98934816657893</v>
+        <v>13.75910950464622</v>
       </c>
     </row>
     <row r="12">
@@ -601,7 +601,7 @@
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>15.46011218136344</v>
+        <v>14.98026030966774</v>
       </c>
     </row>
     <row r="13">
@@ -615,7 +615,7 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>9.479858131497394</v>
+        <v>11.37099444679865</v>
       </c>
     </row>
     <row r="14">
@@ -629,7 +629,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>11.16410625123067</v>
+        <v>11.09632308872643</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +643,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>7.425449405645396</v>
+        <v>10.59657504758284</v>
       </c>
     </row>
     <row r="16">
@@ -657,7 +657,7 @@
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>8.326425089600441</v>
+        <v>11.21615059546542</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +671,7 @@
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>12.71105864072008</v>
+        <v>10.13340031910094</v>
       </c>
     </row>
     <row r="18">
@@ -685,7 +685,7 @@
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>8.732716102179197</v>
+        <v>11.45105579606072</v>
       </c>
     </row>
     <row r="19">
@@ -699,7 +699,7 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>8.27334434794534</v>
+        <v>9.955069301990703</v>
       </c>
     </row>
     <row r="20">
@@ -713,7 +713,7 @@
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>9.836632124632974</v>
+        <v>12.11687461270492</v>
       </c>
     </row>
     <row r="21">
@@ -727,7 +727,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>6.826735557533066</v>
+        <v>11.80588589225555</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>8.097699793111063</v>
+        <v>11.96865823462783</v>
       </c>
     </row>
     <row r="23">
@@ -755,7 +755,7 @@
         <v>15</v>
       </c>
       <c r="D23" t="n">
-        <v>10.07815987208036</v>
+        <v>12.5488957387662</v>
       </c>
     </row>
     <row r="24">
@@ -769,7 +769,7 @@
         <v>14</v>
       </c>
       <c r="D24" t="n">
-        <v>13.50865771278761</v>
+        <v>15.91958474901437</v>
       </c>
     </row>
     <row r="25">
@@ -783,7 +783,7 @@
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>12.45310078929112</v>
+        <v>15.83123950672045</v>
       </c>
     </row>
     <row r="26">
@@ -797,7 +797,7 @@
         <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>11.9605073003629</v>
+        <v>15.90733613716035</v>
       </c>
     </row>
     <row r="27">
@@ -811,7 +811,7 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>11.37946390814199</v>
+        <v>14.54665766729017</v>
       </c>
     </row>
     <row r="28">
@@ -825,7 +825,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>9.593006572376781</v>
+        <v>13.75660563619273</v>
       </c>
     </row>
     <row r="29">
@@ -839,7 +839,7 @@
         <v>14</v>
       </c>
       <c r="D29" t="n">
-        <v>12.65584138859632</v>
+        <v>12.3836423764775</v>
       </c>
     </row>
     <row r="30">
@@ -853,7 +853,7 @@
         <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>11.99789670370732</v>
+        <v>12.45814356645981</v>
       </c>
     </row>
     <row r="31">
@@ -867,7 +867,7 @@
         <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>10.91052544676793</v>
+        <v>11.75202200092951</v>
       </c>
     </row>
     <row r="32">
@@ -881,7 +881,7 @@
         <v>10</v>
       </c>
       <c r="D32" t="n">
-        <v>9.124575542781702</v>
+        <v>12.6113531873534</v>
       </c>
     </row>
   </sheetData>
